--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,28 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LID-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,28 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LID-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Miguel Alvarado</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,28 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LID-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cruz Carreon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,28 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LID-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cruz Carreon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruz Carreon</t>
+          <t>Luis Alvarado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LID-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>David Hernandez</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,28 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LID-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Marvin Flores</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,28 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LID-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jesus Campos</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,28 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LID-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jesús Perez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jesus Morales</t>
+          <t>Jesús Morales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jesus Campos</t>
+          <t>Jesús Campos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jesús Morales</t>
+          <t>Jesus Morales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -455,204 +455,6 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LID-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bryan Flores</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LID-03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LID-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Miguel Alvarado</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LID-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cruz Carreon</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LID-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Luis Alvarado</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LID-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>David Hernandez</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LID-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Marvin Flores</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LID-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jesús Campos</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LID-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Jesús Perez</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,270 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LID-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Miguel Alvarado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LID-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jesús Morales</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LID-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bryan Flors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LID-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Marcin Flores</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LID-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cruz Carreon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LID-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LID-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Uriel Garcia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LID-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Luis Alvarado</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LID-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jesús Campos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LID-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jesús Perez</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LID-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>David Hernandez</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LID-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rodolfo Fernandez</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jesus Morales</t>
+          <t>Practicantes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Practicantes</t>
+          <t>Jesus Morales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bryan Flors</t>
+          <t>Bryan Flores</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marcin Flores</t>
+          <t>Marvin Flores</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Practicantes</t>
+          <t>Jesus Morales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jesus Morales</t>
+          <t>Practicante Dual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/BD_Lideres.xlsx
+++ b/BD_Lideres.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
